--- a/Routine.xlsx
+++ b/Routine.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programming\CODE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6798E802-05A2-4F51-997F-E0E926EB9E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4635C9F-085D-43A1-9FF6-DC5EC1F868D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="12216" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DSA" sheetId="1" r:id="rId1"/>
     <sheet name="Company Names" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="Interview Questions" sheetId="5" r:id="rId4"/>
+    <sheet name="COverage" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Company Names'!$A$1:$A$265</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Company Names'!$A$1:$A$386</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="535">
   <si>
     <t>24th Feb</t>
   </si>
@@ -1507,12 +1509,452 @@
   <si>
     <t>Completed the Linear regression</t>
   </si>
+  <si>
+    <t>17th Mar</t>
+  </si>
+  <si>
+    <t>18th Mar</t>
+  </si>
+  <si>
+    <t>19th Mar</t>
+  </si>
+  <si>
+    <t>20th Mar</t>
+  </si>
+  <si>
+    <t>21st Mar</t>
+  </si>
+  <si>
+    <t>22nd Mar</t>
+  </si>
+  <si>
+    <t>23rd Mar</t>
+  </si>
+  <si>
+    <t>24th Mar</t>
+  </si>
+  <si>
+    <t>25th Mar</t>
+  </si>
+  <si>
+    <t>26th Mar</t>
+  </si>
+  <si>
+    <t>27th Mar</t>
+  </si>
+  <si>
+    <t>28th Mar</t>
+  </si>
+  <si>
+    <t>29th Mar</t>
+  </si>
+  <si>
+    <t>30th Mar</t>
+  </si>
+  <si>
+    <t>31st Mar</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Complete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the Ensemble model and how it is derived
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Complete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the SVC implementation using scikit learn
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Watch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the 3 videos of the BST
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Discuss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on the lambda index, other topics documented in yesterday discussion
+Document the updates
+take baggu key bike</t>
+    </r>
+  </si>
+  <si>
+    <t>gartner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have sent an email </t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/jayveernanda_senior-software-engineer-genai-and-nlp-activity-7330494703278133248-H13G?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAACyQsRMBdDSUWVUDgg4u2x5GCxMPwAP_-Ac</t>
+  </si>
+  <si>
+    <t>applied on 22-05-25</t>
+  </si>
+  <si>
+    <t>EH-FY26-Consulting-AI &amp; Data-Consultant-Machine Learning + Gen AI 
+https://www.linkedin.com/jobs/view/4231826684</t>
+  </si>
+  <si>
+    <t>https://bit.ly/shantanu_resume_ML</t>
+  </si>
+  <si>
+    <t>have texted on Linked</t>
+  </si>
+  <si>
+    <t>1st June</t>
+  </si>
+  <si>
+    <t>2nd June</t>
+  </si>
+  <si>
+    <t>3rd June</t>
+  </si>
+  <si>
+    <t>4th June</t>
+  </si>
+  <si>
+    <t>5th June</t>
+  </si>
+  <si>
+    <t>6th June</t>
+  </si>
+  <si>
+    <t>7th June</t>
+  </si>
+  <si>
+    <t>8th June</t>
+  </si>
+  <si>
+    <t>9th June</t>
+  </si>
+  <si>
+    <t>10th June</t>
+  </si>
+  <si>
+    <t>11th June</t>
+  </si>
+  <si>
+    <t>12th June</t>
+  </si>
+  <si>
+    <t>13th June</t>
+  </si>
+  <si>
+    <t>14th June</t>
+  </si>
+  <si>
+    <t>15th June</t>
+  </si>
+  <si>
+    <t>16th June</t>
+  </si>
+  <si>
+    <t>17th June</t>
+  </si>
+  <si>
+    <t>18th June</t>
+  </si>
+  <si>
+    <t>19th June</t>
+  </si>
+  <si>
+    <t>20th June</t>
+  </si>
+  <si>
+    <t>21st June</t>
+  </si>
+  <si>
+    <t>22nd June</t>
+  </si>
+  <si>
+    <t>23rd June</t>
+  </si>
+  <si>
+    <t>24th June</t>
+  </si>
+  <si>
+    <t>25th June</t>
+  </si>
+  <si>
+    <t>26th June</t>
+  </si>
+  <si>
+    <t>27th June</t>
+  </si>
+  <si>
+    <t>28th June</t>
+  </si>
+  <si>
+    <t>29th June</t>
+  </si>
+  <si>
+    <t>30th June</t>
+  </si>
+  <si>
+    <t>abinbev</t>
+  </si>
+  <si>
+    <t>https://shorturl.at/huHGy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deployment queston, how </t>
+  </si>
+  <si>
+    <t>chunking-size,model, why ?, how to determine the chunking size</t>
+  </si>
+  <si>
+    <t>Vector DB used?</t>
+  </si>
+  <si>
+    <t>Complete platform architecture --aws/azure</t>
+  </si>
+  <si>
+    <t>Ensemble model-how to define a result? Like which one to select when we have same result xgboost vs randomfores</t>
+  </si>
+  <si>
+    <t>when AUC for classfication taksk is same for noth xgboost an randomforest, which model will you select</t>
+  </si>
+  <si>
+    <t>what is difference between chunk size and overlap</t>
+  </si>
+  <si>
+    <t>what is top k and topn</t>
+  </si>
+  <si>
+    <t>what is MMX</t>
+  </si>
+  <si>
+    <t>what is markov chain</t>
+  </si>
+  <si>
+    <t>why linear regression</t>
+  </si>
+  <si>
+    <t>input of the llm</t>
+  </si>
+  <si>
+    <t>what infra did you used for the RAG</t>
+  </si>
+  <si>
+    <t>Which LLM did you used</t>
+  </si>
+  <si>
+    <t>for email intent why we go for LLM, why not bert or normal transformer model</t>
+  </si>
+  <si>
+    <t>how markov chain works</t>
+  </si>
+  <si>
+    <t>get the model detials</t>
+  </si>
+  <si>
+    <t>how many documents were there for the Embedding db</t>
+  </si>
+  <si>
+    <t>how actually designe the evaluation process</t>
+  </si>
+  <si>
+    <t>how many concurrent user were using the application</t>
+  </si>
+  <si>
+    <t>how did you handle the traffic</t>
+  </si>
+  <si>
+    <t>difference between syncro and async</t>
+  </si>
+  <si>
+    <t>how we ensure that the oputput generated by LLM is relevant?</t>
+  </si>
+  <si>
+    <t>Define the architecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">how do you scale fromPOC to deployment,? Like was it done on cluster </t>
+  </si>
+  <si>
+    <t>1st July</t>
+  </si>
+  <si>
+    <t>2nd July</t>
+  </si>
+  <si>
+    <t>3rd July</t>
+  </si>
+  <si>
+    <t>4th July</t>
+  </si>
+  <si>
+    <t>5th July</t>
+  </si>
+  <si>
+    <t>6th July</t>
+  </si>
+  <si>
+    <t>7th July</t>
+  </si>
+  <si>
+    <t>8th July</t>
+  </si>
+  <si>
+    <t>9th July</t>
+  </si>
+  <si>
+    <t>10th July</t>
+  </si>
+  <si>
+    <t>11th July</t>
+  </si>
+  <si>
+    <t>12th July</t>
+  </si>
+  <si>
+    <t>13th July</t>
+  </si>
+  <si>
+    <t>14th July</t>
+  </si>
+  <si>
+    <t>15th July</t>
+  </si>
+  <si>
+    <t>16th July</t>
+  </si>
+  <si>
+    <t>17th July</t>
+  </si>
+  <si>
+    <t>18th July</t>
+  </si>
+  <si>
+    <t>19th July</t>
+  </si>
+  <si>
+    <t>20th July</t>
+  </si>
+  <si>
+    <t>21st July</t>
+  </si>
+  <si>
+    <t>22nd July</t>
+  </si>
+  <si>
+    <t>23rd July</t>
+  </si>
+  <si>
+    <t>24th July</t>
+  </si>
+  <si>
+    <t>25th July</t>
+  </si>
+  <si>
+    <t>26th July</t>
+  </si>
+  <si>
+    <t>27th July</t>
+  </si>
+  <si>
+    <t>28th July</t>
+  </si>
+  <si>
+    <t>29th July</t>
+  </si>
+  <si>
+    <t>30th July</t>
+  </si>
+  <si>
+    <t>31st July</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start from the </t>
+  </si>
+  <si>
+    <t>GenAI</t>
+  </si>
+  <si>
+    <t>Deep Leanring</t>
+  </si>
+  <si>
+    <t>System Desing</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t>aws</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1534,8 +1976,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1545,6 +1995,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1558,10 +2020,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1570,11 +2033,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1853,16 +2322,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:DK15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.6640625" customWidth="1"/>
-    <col min="4" max="4" width="18.88671875" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="7" max="18" width="8.88671875" hidden="1" customWidth="1"/>
+    <col min="19" max="25" width="0" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="29.21875" hidden="1" customWidth="1"/>
+    <col min="27" max="28" width="8.44140625" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="8.21875" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="8.77734375" hidden="1" customWidth="1"/>
+    <col min="31" max="38" width="8.44140625" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="8.21875" hidden="1" customWidth="1"/>
+    <col min="40" max="69" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:115" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -1935,8 +2414,281 @@
       <c r="X1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="Y1" t="s">
+        <v>418</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>419</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="AH1" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="AI1" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="AJ1" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="AK1" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="AL1" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="AM1" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="AN1" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>443</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>444</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>445</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>446</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>447</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>448</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>449</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>451</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>452</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>453</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>454</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>455</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>456</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>457</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>458</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>459</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>460</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>461</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>462</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>463</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>464</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>465</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>466</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>467</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>468</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>469</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>470</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>456</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>457</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>458</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>459</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>460</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>461</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>462</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>463</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>464</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>465</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>466</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>467</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>468</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>469</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>470</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>498</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>499</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>500</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>501</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>502</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>503</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>504</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>505</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>506</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>507</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>508</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>509</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>510</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>511</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>512</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>513</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>514</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>515</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>516</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>517</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>518</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>519</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>520</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>521</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>522</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>523</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>524</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>525</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>526</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>527</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="2" spans="1:115" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1950,17 +2702,20 @@
         <v>31</v>
       </c>
       <c r="W2" s="1"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="BR2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3" spans="1:115" x14ac:dyDescent="0.3">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
       <c r="W3" s="1"/>
     </row>
-    <row r="4" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:115" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -1968,47 +2723,50 @@
         <v>417</v>
       </c>
       <c r="W4" s="1"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Z4" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="5" spans="1:115" x14ac:dyDescent="0.3">
       <c r="W5" s="1"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:115" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="W6" s="1"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:115" x14ac:dyDescent="0.3">
       <c r="W7" s="1"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:115" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="W8" s="1"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:115" x14ac:dyDescent="0.3">
       <c r="W9" s="1"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:115" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
       <c r="W10" s="1"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:115" x14ac:dyDescent="0.3">
       <c r="W11" s="1"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:115" x14ac:dyDescent="0.3">
       <c r="W12" s="1"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:115" x14ac:dyDescent="0.3">
       <c r="W13" s="1"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:115" x14ac:dyDescent="0.3">
       <c r="W14" s="1"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:115" x14ac:dyDescent="0.3">
       <c r="W15" s="1"/>
     </row>
   </sheetData>
@@ -2023,12 +2781,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2938FFF0-599B-4786-9725-823F8C6C7358}">
-  <dimension ref="A1:F384"/>
+  <dimension ref="A1:F386"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -2056,1916 +2815,1961 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>51</v>
+      <c r="A4" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>325</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>396</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>226</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>304</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>190</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>400</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>298</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>298</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>251</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>291</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>380</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>371</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>284</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>378</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>378</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>389</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>312</v>
+        <v>389</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>359</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>359</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>326</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>199</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>307</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>147</v>
+        <v>319</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>209</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>139</v>
+        <v>209</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>333</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>168</v>
+        <v>333</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>292</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>85</v>
+        <v>292</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>316</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>202</v>
+        <v>358</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>153</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>241</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>96</v>
+        <v>241</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>286</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>367</v>
+        <v>286</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>146</v>
+        <v>367</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>328</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>270</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>317</v>
+        <v>270</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>126</v>
+        <v>317</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>59</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>349</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>142</v>
+        <v>362</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>108</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>275</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>191</v>
+        <v>275</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="89" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="B89" t="s">
+        <v>437</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F89" s="5">
+        <v>45799</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>53</v>
+        <v>295</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>272</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>376</v>
+        <v>313</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>248</v>
+        <v>376</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>384</v>
+        <v>248</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>212</v>
+        <v>384</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>93</v>
+        <v>212</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>324</v>
+        <v>93</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>352</v>
+        <v>324</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>170</v>
+        <v>352</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>294</v>
+        <v>162</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>294</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B118" t="s">
+        <v>435</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="F118" s="5">
+        <v>45799</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+      <c r="B139" t="s">
+        <v>440</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="F139" s="6">
+        <v>45799</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
         <v>337</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>69</v>
+        <v>329</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>43</v>
+        <v>235</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>301</v>
+        <v>42</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>238</v>
+        <v>43</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>92</v>
+        <v>238</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>229</v>
+        <v>318</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>261</v>
+        <v>92</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>95</v>
+        <v>229</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>355</v>
+        <v>261</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>289</v>
+        <v>355</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>189</v>
+        <v>131</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>38</v>
+        <v>289</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>305</v>
+        <v>189</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>39</v>
+        <v>305</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>363</v>
+        <v>250</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>385</v>
+        <v>39</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>149</v>
+        <v>385</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>336</v>
+        <v>394</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>392</v>
+        <v>336</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>150</v>
+        <v>97</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>187</v>
+        <v>392</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>390</v>
+        <v>150</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>391</v>
+        <v>187</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>308</v>
+        <v>390</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>253</v>
+        <v>391</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>45</v>
+        <v>322</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>387</v>
+        <v>274</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>264</v>
+        <v>45</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>297</v>
+        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>360</v>
+        <v>297</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>91</v>
+        <v>311</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>285</v>
+        <v>91</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>182</v>
+        <v>351</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>216</v>
+        <v>285</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>375</v>
+        <v>182</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>87</v>
+        <v>216</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>245</v>
+        <v>375</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>320</v>
+        <v>87</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>181</v>
+        <v>245</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>70</v>
+        <v>320</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>344</v>
+        <v>181</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>141</v>
+        <v>344</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>302</v>
+        <v>47</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>265</v>
+        <v>36</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>225</v>
+        <v>302</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>56</v>
+        <v>225</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>267</v>
+        <v>56</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>82</v>
+        <v>267</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>283</v>
+        <v>148</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>350</v>
+        <v>82</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>247</v>
+        <v>350</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>88</v>
+        <v>277</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>330</v>
+        <v>269</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>52</v>
+        <v>330</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>306</v>
+        <v>61</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>339</v>
+        <v>52</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>372</v>
+        <v>306</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>40</v>
+        <v>339</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>309</v>
+        <v>40</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>46</v>
+        <v>370</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>113</v>
+        <v>309</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>135</v>
+        <v>46</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>300</v>
+        <v>113</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>340</v>
+        <v>300</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>222</v>
+        <v>155</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>118</v>
+        <v>340</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>144</v>
+        <v>222</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>335</v>
+        <v>144</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>211</v>
+        <v>84</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>266</v>
+        <v>335</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>345</v>
+        <v>211</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>66</v>
+        <v>266</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>382</v>
+        <v>345</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>217</v>
+        <v>66</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>246</v>
+        <v>382</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>334</v>
+        <v>217</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>112</v>
+        <v>246</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>121</v>
+        <v>334</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>186</v>
+        <v>129</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>310</v>
+        <v>186</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>254</v>
+        <v>310</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>65</v>
+        <v>213</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>369</v>
+        <v>65</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>152</v>
+        <v>242</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>397</v>
+        <v>369</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>105</v>
+        <v>397</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>60</v>
+        <v>200</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>206</v>
+        <v>60</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>151</v>
+        <v>206</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>299</v>
+        <v>151</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>243</v>
+        <v>90</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>356</v>
+        <v>243</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>386</v>
+        <v>273</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>110</v>
+        <v>356</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>111</v>
+        <v>386</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>364</v>
+        <v>110</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>173</v>
+        <v>111</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>280</v>
+        <v>364</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>249</v>
+        <v>173</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>62</v>
+        <v>249</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>75</v>
+        <v>210</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>223</v>
+        <v>62</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>231</v>
+        <v>161</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>102</v>
+        <v>218</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>67</v>
+        <v>172</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>255</v>
+        <v>169</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>342</v>
+        <v>255</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>207</v>
+        <v>342</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>227</v>
+        <v>64</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>117</v>
+        <v>227</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>398</v>
+        <v>239</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>259</v>
+        <v>117</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>296</v>
+        <v>398</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>388</v>
+        <v>259</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>374</v>
+        <v>296</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>263</v>
+        <v>374</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>315</v>
+        <v>393</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>140</v>
+        <v>315</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>321</v>
+        <v>197</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>287</v>
+        <v>140</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>244</v>
+        <v>321</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>98</v>
+        <v>244</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>160</v>
+        <v>240</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>208</v>
+        <v>98</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>377</v>
+        <v>160</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>63</v>
+        <v>208</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>50</v>
+        <v>377</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>288</v>
+        <v>72</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>233</v>
+        <v>106</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>145</v>
+        <v>288</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>338</v>
+        <v>83</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>323</v>
+        <v>86</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>193</v>
+        <v>323</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>290</v>
+        <v>332</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>136</v>
+        <v>290</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>361</v>
+        <v>119</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>178</v>
+        <v>361</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>293</v>
+        <v>44</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>74</v>
+        <v>232</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>236</v>
+        <v>123</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>282</v>
+        <v>74</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>163</v>
+        <v>366</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>167</v>
+        <v>252</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>271</v>
+        <v>163</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>79</v>
+        <v>167</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>71</v>
+        <v>271</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>198</v>
+        <v>79</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>234</v>
+        <v>71</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>58</v>
+        <v>198</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>68</v>
+        <v>234</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>347</v>
+        <v>68</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>203</v>
+        <v>347</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>405</v>
+        <v>214</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>406</v>
+        <v>228</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
         <v>415</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A362" xr:uid="{2938FFF0-599B-4786-9725-823F8C6C7358}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A369">
-      <sortCondition ref="A1:A362"/>
+  <autoFilter ref="A1:A386" xr:uid="{2938FFF0-599B-4786-9725-823F8C6C7358}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A371">
+      <sortCondition ref="A1:A364"/>
     </sortState>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="C118" r:id="rId1" xr:uid="{6A344644-51F3-425A-BC26-94B29CFCDFD2}"/>
+    <hyperlink ref="C139" r:id="rId2" xr:uid="{F7CC7C41-FDBE-46AB-ACCB-957E2FAE0DD8}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{0CA201F3-3A8A-4B0F-958F-C771FE0F60EC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3986,4 +4790,180 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49604235-DC0E-44D7-A7E9-3841F03810F7}">
+  <dimension ref="A1:A27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="53.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>497</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7C1996-BA63-4431-9363-F212C9C8FEA1}">
+  <dimension ref="B2:V2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>530</v>
+      </c>
+      <c r="K2" t="s">
+        <v>531</v>
+      </c>
+      <c r="N2" t="s">
+        <v>532</v>
+      </c>
+      <c r="R2" t="s">
+        <v>533</v>
+      </c>
+      <c r="V2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>